--- a/zara周报数据源/日度数据整体/0310-0316_zara日度数据.xlsx
+++ b/zara周报数据源/日度数据整体/0310-0316_zara日度数据.xlsx
@@ -474,7 +474,6 @@
       <c t="str">
         <v>应用的筛选器: 
 Date 在 2026/3/10 当天或之后 和 在 2026/3/17 之前
-搜索是否有结果 等于 有结果
 handlemodule 不等于 推荐产品
 品牌名 等于 ZARA
 渠道来源 不等于 (空白)</v>
@@ -559,68 +558,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c/>
       <c s="6">
-        <v>38270</v>
+        <v>47706</v>
       </c>
       <c s="7">
-        <v>12680</v>
+        <v>15387</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>44862</v>
+        <v>49944</v>
       </c>
       <c s="10">
-        <v>10086</v>
+        <v>11794</v>
       </c>
       <c s="11">
-        <v>0.795425867507886</v>
+        <v>0.766491193864951</v>
       </c>
       <c s="12">
-        <v>8281</v>
+        <v>9961</v>
       </c>
       <c s="13">
-        <v>4003</v>
+        <v>4980</v>
       </c>
       <c s="14">
-        <v>0.315694006309148</v>
+        <v>0.323649834275687</v>
       </c>
       <c s="15">
-        <v>0.396886773745786</v>
+        <v>0.422248600983551</v>
       </c>
       <c s="16">
-        <v>671</v>
+        <v>759</v>
       </c>
       <c s="17">
-        <v>583</v>
+        <v>670</v>
       </c>
       <c s="18">
-        <v>0.0459779179810726</v>
+        <v>0.0435432507961266</v>
       </c>
       <c s="19">
-        <v>0.0578028951021218</v>
+        <v>0.0568085467186705</v>
       </c>
       <c s="20">
-        <v>0.145640769422933</v>
+        <v>0.134538152610442</v>
       </c>
       <c s="21">
-        <v>1.15094339622642</v>
+        <v>1.13283582089552</v>
       </c>
       <c s="22">
-        <v>4.44794765020821</v>
+        <v>4.23469560793624</v>
       </c>
       <c s="23">
-        <v>2.06869847614289</v>
+        <v>2.00020080321285</v>
       </c>
       <c s="24">
-        <v>3.01813880126183</v>
+        <v>3.10040943653734</v>
       </c>
       <c s="25">
-        <v>278724</v>
+        <v>328779</v>
       </c>
     </row>
     <row r="5">
@@ -628,68 +627,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c/>
       <c s="6">
-        <v>43228</v>
+        <v>41844</v>
       </c>
       <c s="7">
-        <v>14648</v>
+        <v>13252</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>49802</v>
+        <v>45039</v>
       </c>
       <c s="10">
-        <v>11764</v>
+        <v>10125</v>
       </c>
       <c s="11">
-        <v>0.803113052976516</v>
+        <v>0.764035617265318</v>
       </c>
       <c s="12">
-        <v>9933</v>
+        <v>8308</v>
       </c>
       <c s="13">
-        <v>4969</v>
+        <v>4012</v>
       </c>
       <c s="14">
-        <v>0.339227198252321</v>
+        <v>0.302746755206761</v>
       </c>
       <c s="15">
-        <v>0.422390343420605</v>
+        <v>0.396246913580247</v>
       </c>
       <c s="16">
-        <v>754</v>
+        <v>672</v>
       </c>
       <c s="17">
-        <v>665</v>
+        <v>584</v>
       </c>
       <c s="18">
-        <v>0.045398689240852</v>
+        <v>0.0440688198007848</v>
       </c>
       <c s="19">
-        <v>0.0565283917035022</v>
+        <v>0.057679012345679</v>
       </c>
       <c s="20">
-        <v>0.133829744415375</v>
+        <v>0.145563310069791</v>
       </c>
       <c s="21">
-        <v>1.13383458646617</v>
+        <v>1.15068493150685</v>
       </c>
       <c s="22">
-        <v>4.23342400544033</v>
+        <v>4.4482962962963</v>
       </c>
       <c s="23">
-        <v>1.99899376132019</v>
+        <v>2.07078763708873</v>
       </c>
       <c s="24">
-        <v>2.95111960677226</v>
+        <v>3.15756112284938</v>
       </c>
       <c s="25">
-        <v>327724</v>
+        <v>278953</v>
       </c>
     </row>
     <row r="6">
@@ -697,68 +696,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46095</v>
+        <v>46091</v>
       </c>
       <c/>
       <c s="6">
-        <v>40905</v>
+        <v>38651</v>
       </c>
       <c s="7">
-        <v>13239</v>
+        <v>12101</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>45928</v>
+        <v>40226</v>
       </c>
       <c s="10">
-        <v>10188</v>
+        <v>9188</v>
       </c>
       <c s="11">
-        <v>0.769544527532291</v>
+        <v>0.759276092884886</v>
       </c>
       <c s="12">
-        <v>8624</v>
+        <v>7424</v>
       </c>
       <c s="13">
-        <v>4060</v>
+        <v>3359</v>
       </c>
       <c s="14">
-        <v>0.306669688042904</v>
+        <v>0.277580365259069</v>
       </c>
       <c s="15">
-        <v>0.398508048684727</v>
+        <v>0.365585546364824</v>
       </c>
       <c s="16">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c s="17">
-        <v>553</v>
+        <v>516</v>
       </c>
       <c s="18">
-        <v>0.0417705264748093</v>
+        <v>0.0426411040409884</v>
       </c>
       <c s="19">
-        <v>0.0542795445622301</v>
+        <v>0.0561602089682194</v>
       </c>
       <c s="20">
-        <v>0.136206896551724</v>
+        <v>0.153617147960703</v>
       </c>
       <c s="21">
-        <v>1.14828209764919</v>
+        <v>1.18217054263566</v>
       </c>
       <c s="22">
-        <v>4.50804868472713</v>
+        <v>4.37810187200697</v>
       </c>
       <c s="23">
-        <v>2.12413793103448</v>
+        <v>2.21018160166716</v>
       </c>
       <c s="24">
-        <v>3.08973487423521</v>
+        <v>3.1940335509462</v>
       </c>
       <c s="25">
-        <v>275444</v>
+        <v>254040</v>
       </c>
     </row>
     <row r="7">
@@ -766,68 +765,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c/>
       <c s="6">
-        <v>34848</v>
+        <v>36579</v>
       </c>
       <c s="7">
-        <v>11569</v>
+        <v>11649</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>38516</v>
+        <v>38563</v>
       </c>
       <c s="10">
-        <v>8792</v>
+        <v>8621</v>
       </c>
       <c s="11">
-        <v>0.759961967326476</v>
+        <v>0.740063524766074</v>
       </c>
       <c s="12">
-        <v>7249</v>
+        <v>6572</v>
       </c>
       <c s="13">
-        <v>3254</v>
+        <v>3155</v>
       </c>
       <c s="14">
-        <v>0.281268908289394</v>
+        <v>0.270838698600738</v>
       </c>
       <c s="15">
-        <v>0.370109190172884</v>
+        <v>0.365966825194293</v>
       </c>
       <c s="16">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c s="17">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c s="18">
-        <v>0.0384648629959374</v>
+        <v>0.0412052536698429</v>
       </c>
       <c s="19">
-        <v>0.050614194722475</v>
+        <v>0.0556779955921587</v>
       </c>
       <c s="20">
-        <v>0.136754763368162</v>
+        <v>0.152139461172742</v>
       </c>
       <c s="21">
-        <v>1.21797752808989</v>
+        <v>1.13125</v>
       </c>
       <c s="22">
-        <v>4.38080072793449</v>
+        <v>4.4731469667092</v>
       </c>
       <c s="23">
-        <v>2.22771972956361</v>
+        <v>2.08304278922345</v>
       </c>
       <c s="24">
-        <v>3.01218774310658</v>
+        <v>3.14009786247747</v>
       </c>
       <c s="25">
-        <v>234875</v>
+        <v>210154</v>
       </c>
     </row>
     <row r="8">
@@ -835,68 +834,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46093</v>
+        <v>46095</v>
       </c>
       <c/>
       <c s="6">
-        <v>35548</v>
+        <v>44881</v>
       </c>
       <c s="7">
-        <v>11888</v>
+        <v>13875</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>41919</v>
+        <v>46076</v>
       </c>
       <c s="10">
-        <v>9196</v>
+        <v>10233</v>
       </c>
       <c s="11">
-        <v>0.773553162853297</v>
+        <v>0.737513513513513</v>
       </c>
       <c s="12">
-        <v>8483</v>
+        <v>8654</v>
       </c>
       <c s="13">
-        <v>3442</v>
+        <v>4083</v>
       </c>
       <c s="14">
-        <v>0.289535666218035</v>
+        <v>0.29427027027027</v>
       </c>
       <c s="15">
-        <v>0.374293170943889</v>
+        <v>0.399003224860745</v>
       </c>
       <c s="16">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c s="17">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c s="18">
-        <v>0.045171601615074</v>
+        <v>0.0400720720720721</v>
       </c>
       <c s="19">
-        <v>0.0583949543279687</v>
+        <v>0.0543340173947034</v>
       </c>
       <c s="20">
-        <v>0.156013945380593</v>
+        <v>0.13617438158217</v>
       </c>
       <c s="21">
-        <v>1.19366852886406</v>
+        <v>1.14748201438849</v>
       </c>
       <c s="22">
-        <v>4.55839495432797</v>
+        <v>4.50268738395387</v>
       </c>
       <c s="23">
-        <v>2.46455549099361</v>
+        <v>2.11951996081313</v>
       </c>
       <c s="24">
-        <v>2.99024226110363</v>
+        <v>3.23466666666667</v>
       </c>
       <c s="25">
-        <v>242238</v>
+        <v>276601</v>
       </c>
     </row>
     <row r="9">
@@ -904,68 +903,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c/>
       <c s="6">
-        <v>33252</v>
+        <v>39246</v>
       </c>
       <c s="7">
-        <v>11048</v>
+        <v>12553</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>38441</v>
+        <v>42078</v>
       </c>
       <c s="10">
-        <v>8578</v>
+        <v>9245</v>
       </c>
       <c s="11">
-        <v>0.776430123099203</v>
+        <v>0.736477336094957</v>
       </c>
       <c s="12">
-        <v>6556</v>
+        <v>8517</v>
       </c>
       <c s="13">
-        <v>3148</v>
+        <v>3459</v>
       </c>
       <c s="14">
-        <v>0.284938450398262</v>
+        <v>0.27555166095754</v>
       </c>
       <c s="15">
-        <v>0.366985311261366</v>
+        <v>0.374148188209843</v>
       </c>
       <c s="16">
+        <v>646</v>
+      </c>
+      <c s="17">
         <v>540</v>
       </c>
-      <c s="17">
-        <v>477</v>
-      </c>
       <c s="18">
-        <v>0.0431752353367125</v>
+        <v>0.043017605353302</v>
       </c>
       <c s="19">
-        <v>0.055607367684775</v>
+        <v>0.0584099513250406</v>
       </c>
       <c s="20">
-        <v>0.151524777636595</v>
+        <v>0.1561144839549</v>
       </c>
       <c s="21">
-        <v>1.13207547169811</v>
+        <v>1.1962962962963</v>
       </c>
       <c s="22">
-        <v>4.481347633481</v>
+        <v>4.55143320713899</v>
       </c>
       <c s="23">
-        <v>2.08259212198221</v>
+        <v>2.46227233304423</v>
       </c>
       <c s="24">
-        <v>3.0097755249819</v>
+        <v>3.12642396239943</v>
       </c>
       <c s="25">
-        <v>209367</v>
+        <v>243813</v>
       </c>
     </row>
     <row r="10">
@@ -973,68 +972,68 @@
         <v>26.03.10~26.03.16</v>
       </c>
       <c s="1">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c/>
       <c s="6">
-        <v>35066</v>
+        <v>39127</v>
       </c>
       <c s="7">
-        <v>11497</v>
+        <v>12483</v>
       </c>
       <c s="8">
         <v>0</v>
       </c>
       <c s="9">
-        <v>39971</v>
+        <v>38679</v>
       </c>
       <c s="10">
-        <v>9070</v>
+        <v>8843</v>
       </c>
       <c s="11">
-        <v>0.78890145255284</v>
+        <v>0.708403428662982</v>
       </c>
       <c s="12">
-        <v>7380</v>
+        <v>7280</v>
       </c>
       <c s="13">
-        <v>3343</v>
+        <v>3268</v>
       </c>
       <c s="14">
-        <v>0.290771505610159</v>
+        <v>0.26179604261796</v>
       </c>
       <c s="15">
-        <v>0.368577728776185</v>
+        <v>0.36955784236119</v>
       </c>
       <c s="16">
-        <v>608</v>
+        <v>545</v>
       </c>
       <c s="17">
-        <v>515</v>
+        <v>448</v>
       </c>
       <c s="18">
-        <v>0.0447942941636949</v>
+        <v>0.0358888087799407</v>
       </c>
       <c s="19">
-        <v>0.0567805953693495</v>
+        <v>0.0506615402012892</v>
       </c>
       <c s="20">
-        <v>0.154053245587795</v>
+        <v>0.137086903304774</v>
       </c>
       <c s="21">
-        <v>1.18058252427184</v>
+        <v>1.21651785714286</v>
       </c>
       <c s="22">
-        <v>4.40694597574421</v>
+        <v>4.37396811036978</v>
       </c>
       <c s="23">
-        <v>2.20759796589889</v>
+        <v>2.22766217870257</v>
       </c>
       <c s="24">
-        <v>3.0500130468818</v>
+        <v>3.13442281502844</v>
       </c>
       <c s="25">
-        <v>253287</v>
+        <v>236038</v>
       </c>
     </row>
   </sheetData>
